--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,82 +23,31 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Date of Joining</t>
-  </si>
-  <si>
-    <t>Worker Type</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Department</t>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
-  <si>
-    <t>PAN Number</t>
-  </si>
-  <si>
-    <t>Payroll Month</t>
-  </si>
-  <si>
-    <t>Actual Payable days</t>
-  </si>
-  <si>
-    <t>Working days</t>
-  </si>
-  <si>
-    <t>Loss of Pay days</t>
-  </si>
-  <si>
-    <t>Days Payable</t>
-  </si>
-  <si>
-    <t>Gross Salary</t>
-  </si>
-  <si>
-    <t>Deduction</t>
-  </si>
-  <si>
-    <t>Net Pay</t>
-  </si>
-  <si>
-    <t>Shubham Retest</t>
-  </si>
-  <si>
-    <t>0001-04-01</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Admin</t>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>Retest</t>
+  </si>
+  <si>
+    <t>North Corp Software</t>
   </si>
   <si>
     <t>Guru Gram</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>1995-09-05</t>
-  </si>
-  <si>
-    <t>ABCYZ1234R</t>
-  </si>
-  <si>
-    <t>BetchOne</t>
   </si>
 </sst>
 </file>
@@ -438,10 +387,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,44 +412,8 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>98</v>
       </c>
@@ -508,52 +421,19 @@
         <v>6386392</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
-        <v>30</v>
-      </c>
-      <c r="N2">
-        <v>20</v>
-      </c>
-      <c r="O2">
-        <v>20</v>
-      </c>
-      <c r="P2">
         <v>10</v>
       </c>
-      <c r="Q2">
+      <c r="G2">
         <v>15000.0</v>
-      </c>
-      <c r="R2">
-        <v>10000.5</v>
-      </c>
-      <c r="S2">
-        <v>4999.5</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Unique ID</t>
   </si>
@@ -35,19 +35,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>salary</t>
-  </si>
-  <si>
-    <t>Shubham</t>
-  </si>
-  <si>
-    <t>Retest</t>
-  </si>
-  <si>
-    <t>North Corp Software</t>
+    <t>bonus</t>
+  </si>
+  <si>
+    <t>test emp</t>
+  </si>
+  <si>
+    <t>test emp last</t>
+  </si>
+  <si>
+    <t>ABC &amp; Company Ltd.</t>
   </si>
   <si>
     <t>Guru Gram</t>
+  </si>
+  <si>
+    <t>devansh</t>
   </si>
 </sst>
 </file>
@@ -387,7 +390,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -415,10 +418,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B2">
-        <v>6386392</v>
+        <v>3609503</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -433,7 +436,30 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>15000.0</v>
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>7026803</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,34 +23,100 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Company</t>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Date of Joining</t>
+  </si>
+  <si>
+    <t>Worker Type</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Department</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>bonus</t>
-  </si>
-  <si>
-    <t>test emp</t>
-  </si>
-  <si>
-    <t>test emp last</t>
-  </si>
-  <si>
-    <t>ABC &amp; Company Ltd.</t>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>PAN Number</t>
+  </si>
+  <si>
+    <t>Payroll Month</t>
+  </si>
+  <si>
+    <t>Actual Payable days</t>
+  </si>
+  <si>
+    <t>Working days</t>
+  </si>
+  <si>
+    <t>Loss of Pay days</t>
+  </si>
+  <si>
+    <t>Days Payable</t>
+  </si>
+  <si>
+    <t>Gross Salary</t>
+  </si>
+  <si>
+    <t>Deduction</t>
+  </si>
+  <si>
+    <t>Net Pay</t>
+  </si>
+  <si>
+    <t>test emp test emp last</t>
+  </si>
+  <si>
+    <t>2024-06-13</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>other</t>
   </si>
   <si>
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>devansh</t>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>ABCTY1234D</t>
+  </si>
+  <si>
+    <t>Finalbatch</t>
+  </si>
+  <si>
+    <t>devansh devansh</t>
+  </si>
+  <si>
+    <t>2024-06-29</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Team Member</t>
+  </si>
+  <si>
+    <t>2024-06-27</t>
+  </si>
+  <si>
+    <t>GKBPD2457K</t>
   </si>
 </sst>
 </file>
@@ -390,10 +456,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,8 +481,44 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>80</v>
       </c>
@@ -424,22 +526,55 @@
         <v>3609503</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>20</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2">
         <v>10</v>
       </c>
-      <c r="G2">
-        <v>500.0</v>
+      <c r="Q2">
+        <v>70000.0</v>
+      </c>
+      <c r="R2">
+        <v>100.0</v>
+      </c>
+      <c r="S2">
+        <v>69900.0</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>100</v>
       </c>
@@ -447,19 +582,52 @@
         <v>7026803</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
+      </c>
+      <c r="O3">
+        <v>20</v>
+      </c>
+      <c r="P3">
         <v>10</v>
       </c>
-      <c r="G3">
-        <v>0.0</v>
+      <c r="Q3">
+        <v>130000.0</v>
+      </c>
+      <c r="R3">
+        <v>86671.0</v>
+      </c>
+      <c r="S3">
+        <v>43329.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>Unique ID</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>Days Payable</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Overtime</t>
   </si>
   <si>
     <t>Gross Salary</t>
@@ -456,10 +468,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,8 +529,20 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>80</v>
       </c>
@@ -526,31 +550,31 @@
         <v>3609503</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M2">
         <v>30</v>
@@ -568,13 +592,22 @@
         <v>70000.0</v>
       </c>
       <c r="R2">
+        <v>700.0</v>
+      </c>
+      <c r="S2">
+        <v>800.0</v>
+      </c>
+      <c r="T2">
+        <v>1000</v>
+      </c>
+      <c r="V2">
         <v>100.0</v>
       </c>
-      <c r="S2">
-        <v>69900.0</v>
+      <c r="W2">
+        <v>71400.0</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>100</v>
       </c>
@@ -582,31 +615,31 @@
         <v>7026803</v>
       </c>
       <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
         <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
       </c>
       <c r="M3">
         <v>30</v>
@@ -624,10 +657,19 @@
         <v>130000.0</v>
       </c>
       <c r="R3">
+        <v>0.0</v>
+      </c>
+      <c r="S3">
+        <v>1000.0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="V3">
         <v>86671.0</v>
       </c>
-      <c r="S3">
-        <v>43329.0</v>
+      <c r="W3">
+        <v>44329.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,112 +23,34 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Date of Joining</t>
-  </si>
-  <si>
-    <t>Worker Type</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Department</t>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
-  <si>
-    <t>PAN Number</t>
-  </si>
-  <si>
-    <t>Payroll Month</t>
-  </si>
-  <si>
-    <t>Actual Payable days</t>
-  </si>
-  <si>
-    <t>Working days</t>
-  </si>
-  <si>
-    <t>Loss of Pay days</t>
-  </si>
-  <si>
-    <t>Days Payable</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-  <si>
-    <t>Bonus</t>
-  </si>
-  <si>
-    <t>Overtime</t>
-  </si>
-  <si>
-    <t>Gross Salary</t>
-  </si>
-  <si>
-    <t>Deduction</t>
-  </si>
-  <si>
-    <t>Net Pay</t>
-  </si>
-  <si>
-    <t>test emp test emp last</t>
-  </si>
-  <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>other</t>
+    <t>retroactive_pay</t>
+  </si>
+  <si>
+    <t>test emp</t>
+  </si>
+  <si>
+    <t>test emp last</t>
+  </si>
+  <si>
+    <t>ABC &amp; Company Ltd.</t>
   </si>
   <si>
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>ABCTY1234D</t>
-  </si>
-  <si>
-    <t>Finalbatch</t>
-  </si>
-  <si>
-    <t>devansh devansh</t>
-  </si>
-  <si>
-    <t>2024-06-29</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Team Member</t>
-  </si>
-  <si>
-    <t>2024-06-27</t>
-  </si>
-  <si>
-    <t>GKBPD2457K</t>
+    <t>devansh</t>
   </si>
 </sst>
 </file>
@@ -468,10 +390,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,56 +415,8 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>80</v>
       </c>
@@ -550,64 +424,22 @@
         <v>3609503</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2">
-        <v>30</v>
-      </c>
-      <c r="N2">
-        <v>20</v>
-      </c>
-      <c r="O2">
-        <v>20</v>
-      </c>
-      <c r="P2">
         <v>10</v>
       </c>
-      <c r="Q2">
-        <v>70000.0</v>
-      </c>
-      <c r="R2">
-        <v>700.0</v>
-      </c>
-      <c r="S2">
-        <v>800.0</v>
-      </c>
-      <c r="T2">
-        <v>1000</v>
-      </c>
-      <c r="V2">
-        <v>100.0</v>
-      </c>
-      <c r="W2">
-        <v>71400.0</v>
+      <c r="G2">
+        <v>0.0</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>100</v>
       </c>
@@ -615,61 +447,19 @@
         <v>7026803</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
-      <c r="N3">
-        <v>20</v>
-      </c>
-      <c r="O3">
-        <v>20</v>
-      </c>
-      <c r="P3">
         <v>10</v>
       </c>
-      <c r="Q3">
-        <v>130000.0</v>
-      </c>
-      <c r="R3">
+      <c r="G3">
         <v>0.0</v>
-      </c>
-      <c r="S3">
-        <v>1000.0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>86671.0</v>
-      </c>
-      <c r="W3">
-        <v>44329.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,34 +23,118 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Company</t>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Date of Joining</t>
+  </si>
+  <si>
+    <t>Worker Type</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Department</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>retroactive_pay</t>
-  </si>
-  <si>
-    <t>test emp</t>
-  </si>
-  <si>
-    <t>test emp last</t>
-  </si>
-  <si>
-    <t>ABC &amp; Company Ltd.</t>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>PAN Number</t>
+  </si>
+  <si>
+    <t>Payroll Month</t>
+  </si>
+  <si>
+    <t>Actual Payable days</t>
+  </si>
+  <si>
+    <t>Working days</t>
+  </si>
+  <si>
+    <t>Loss of Pay days</t>
+  </si>
+  <si>
+    <t>Days Payable</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Overtime</t>
+  </si>
+  <si>
+    <t>Shift Differential</t>
+  </si>
+  <si>
+    <t>Retroactive Pay</t>
+  </si>
+  <si>
+    <t>Gross Wages</t>
+  </si>
+  <si>
+    <t>Deduction</t>
+  </si>
+  <si>
+    <t>Net Pay</t>
+  </si>
+  <si>
+    <t>test emp test emp last</t>
+  </si>
+  <si>
+    <t>2024-06-13</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>other</t>
   </si>
   <si>
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>devansh</t>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>ABCTY1234D</t>
+  </si>
+  <si>
+    <t>Finalbatch</t>
+  </si>
+  <si>
+    <t>devansh devansh</t>
+  </si>
+  <si>
+    <t>2024-06-29</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Team Member</t>
+  </si>
+  <si>
+    <t>2024-06-27</t>
+  </si>
+  <si>
+    <t>GKBPD2457K</t>
   </si>
 </sst>
 </file>
@@ -390,10 +474,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,8 +499,62 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:25">
       <c r="A2">
         <v>80</v>
       </c>
@@ -424,22 +562,73 @@
         <v>3609503</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>20</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="Q2">
+        <v>70000.0</v>
+      </c>
+      <c r="R2">
+        <v>700.0</v>
+      </c>
+      <c r="S2">
+        <v>800.0</v>
+      </c>
+      <c r="T2">
+        <v>1000</v>
+      </c>
+      <c r="U2">
         <v>0.0</v>
       </c>
+      <c r="V2">
+        <v>100.0</v>
+      </c>
+      <c r="W2">
+        <v>72600.0</v>
+      </c>
+      <c r="X2">
+        <v>100.0</v>
+      </c>
+      <c r="Y2">
+        <v>72500.0</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:25">
       <c r="A3">
         <v>100</v>
       </c>
@@ -447,19 +636,70 @@
         <v>7026803</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
+      </c>
+      <c r="O3">
+        <v>20</v>
+      </c>
+      <c r="P3">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="Q3">
+        <v>130000.0</v>
+      </c>
+      <c r="R3">
         <v>0.0</v>
+      </c>
+      <c r="S3">
+        <v>1000.0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.0</v>
+      </c>
+      <c r="V3">
+        <v>100.0</v>
+      </c>
+      <c r="W3">
+        <v>131100.0</v>
+      </c>
+      <c r="X3">
+        <v>86671.0</v>
+      </c>
+      <c r="Y3">
+        <v>44429.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,118 +23,34 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Date of Joining</t>
-  </si>
-  <si>
-    <t>Worker Type</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Department</t>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
-  <si>
-    <t>PAN Number</t>
-  </si>
-  <si>
-    <t>Payroll Month</t>
-  </si>
-  <si>
-    <t>Actual Payable days</t>
-  </si>
-  <si>
-    <t>Working days</t>
-  </si>
-  <si>
-    <t>Loss of Pay days</t>
-  </si>
-  <si>
-    <t>Days Payable</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-  <si>
-    <t>Bonus</t>
-  </si>
-  <si>
-    <t>Overtime</t>
-  </si>
-  <si>
-    <t>Shift Differential</t>
-  </si>
-  <si>
-    <t>Retroactive Pay</t>
-  </si>
-  <si>
-    <t>Gross Wages</t>
-  </si>
-  <si>
-    <t>Deduction</t>
-  </si>
-  <si>
-    <t>Net Pay</t>
-  </si>
-  <si>
-    <t>test emp test emp last</t>
-  </si>
-  <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>other</t>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>test emp</t>
+  </si>
+  <si>
+    <t>test emp last</t>
+  </si>
+  <si>
+    <t>ABC &amp; Company Ltd.</t>
   </si>
   <si>
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>ABCTY1234D</t>
-  </si>
-  <si>
-    <t>Finalbatch</t>
-  </si>
-  <si>
-    <t>devansh devansh</t>
-  </si>
-  <si>
-    <t>2024-06-29</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Team Member</t>
-  </si>
-  <si>
-    <t>2024-06-27</t>
-  </si>
-  <si>
-    <t>GKBPD2457K</t>
+    <t>devansh</t>
   </si>
 </sst>
 </file>
@@ -474,10 +390,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,62 +415,8 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>80</v>
       </c>
@@ -562,73 +424,22 @@
         <v>3609503</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2">
-        <v>30</v>
-      </c>
-      <c r="N2">
-        <v>20</v>
-      </c>
-      <c r="O2">
-        <v>20</v>
-      </c>
-      <c r="P2">
         <v>10</v>
       </c>
-      <c r="Q2">
+      <c r="G2">
         <v>70000.0</v>
       </c>
-      <c r="R2">
-        <v>700.0</v>
-      </c>
-      <c r="S2">
-        <v>800.0</v>
-      </c>
-      <c r="T2">
-        <v>1000</v>
-      </c>
-      <c r="U2">
-        <v>0.0</v>
-      </c>
-      <c r="V2">
-        <v>100.0</v>
-      </c>
-      <c r="W2">
-        <v>72600.0</v>
-      </c>
-      <c r="X2">
-        <v>100.0</v>
-      </c>
-      <c r="Y2">
-        <v>72500.0</v>
-      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>100</v>
       </c>
@@ -636,70 +447,19 @@
         <v>7026803</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
-      <c r="N3">
-        <v>20</v>
-      </c>
-      <c r="O3">
-        <v>20</v>
-      </c>
-      <c r="P3">
         <v>10</v>
       </c>
-      <c r="Q3">
+      <c r="G3">
         <v>130000.0</v>
-      </c>
-      <c r="R3">
-        <v>0.0</v>
-      </c>
-      <c r="S3">
-        <v>1000.0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.0</v>
-      </c>
-      <c r="V3">
-        <v>100.0</v>
-      </c>
-      <c r="W3">
-        <v>131100.0</v>
-      </c>
-      <c r="X3">
-        <v>86671.0</v>
-      </c>
-      <c r="Y3">
-        <v>44429.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <si>
     <t>Unique ID</t>
   </si>
@@ -35,13 +35,13 @@
     <t>Location</t>
   </si>
   <si>
-    <t>salary</t>
-  </si>
-  <si>
-    <t>test emp</t>
-  </si>
-  <si>
-    <t>test emp last</t>
+    <t>bonus</t>
+  </si>
+  <si>
+    <t>Suraj</t>
+  </si>
+  <si>
+    <t>Singh</t>
   </si>
   <si>
     <t>ABC &amp; Company Ltd.</t>
@@ -50,7 +50,43 @@
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>devansh</t>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Bangluru</t>
+  </si>
+  <si>
+    <t>Nikhil</t>
+  </si>
+  <si>
+    <t>Saini</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>yadav</t>
+  </si>
+  <si>
+    <t>vaibhav</t>
+  </si>
+  <si>
+    <t>kumar</t>
+  </si>
+  <si>
+    <t>Nayan</t>
+  </si>
+  <si>
+    <t>Ganguly</t>
+  </si>
+  <si>
+    <t>North Corp Software</t>
   </si>
 </sst>
 </file>
@@ -390,7 +426,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -418,10 +454,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>3609503</v>
+        <v>120176</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -436,30 +472,122 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>70000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>7026803</v>
+        <v>141151</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>57</v>
+      </c>
+      <c r="B4">
+        <v>9150391</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>133843</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="G3">
-        <v>130000.0</v>
+      <c r="G5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>72</v>
+      </c>
+      <c r="B6">
+        <v>7821991</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>214390</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -35,7 +35,7 @@
     <t>Location</t>
   </si>
   <si>
-    <t>bonus</t>
+    <t>commission</t>
   </si>
   <si>
     <t>Suraj</t>

--- a/public/uploads/batch.xlsx
+++ b/public/uploads/batch.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
   <si>
     <t>Unique ID</t>
   </si>
@@ -23,70 +23,106 @@
     <t>EMP ID</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Company</t>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Date of Joining</t>
+  </si>
+  <si>
+    <t>Worker Type</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Department</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>commission</t>
-  </si>
-  <si>
-    <t>Suraj</t>
-  </si>
-  <si>
-    <t>Singh</t>
-  </si>
-  <si>
-    <t>ABC &amp; Company Ltd.</t>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>PAN Number</t>
+  </si>
+  <si>
+    <t>Payroll Month</t>
+  </si>
+  <si>
+    <t>Actual Payable days</t>
+  </si>
+  <si>
+    <t>Working days</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Loss of Pay days</t>
+  </si>
+  <si>
+    <t>Days Payable</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Overtime</t>
+  </si>
+  <si>
+    <t>Shift Differential</t>
+  </si>
+  <si>
+    <t>Retroactive Pay</t>
+  </si>
+  <si>
+    <t>Gross Wages</t>
+  </si>
+  <si>
+    <t>Deduction</t>
+  </si>
+  <si>
+    <t>Net Pay</t>
+  </si>
+  <si>
+    <t>Atul Singh</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Quality Testing</t>
   </si>
   <si>
     <t>Guru Gram</t>
   </si>
   <si>
-    <t>Shubham</t>
-  </si>
-  <si>
-    <t>Sharma</t>
-  </si>
-  <si>
-    <t>Bangluru</t>
-  </si>
-  <si>
-    <t>Nikhil</t>
-  </si>
-  <si>
-    <t>Saini</t>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>Rohit</t>
-  </si>
-  <si>
-    <t>yadav</t>
-  </si>
-  <si>
-    <t>vaibhav</t>
-  </si>
-  <si>
-    <t>kumar</t>
-  </si>
-  <si>
-    <t>Nayan</t>
-  </si>
-  <si>
-    <t>Ganguly</t>
-  </si>
-  <si>
-    <t>North Corp Software</t>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2014-06-04</t>
+  </si>
+  <si>
+    <t>BCDEF2345G</t>
+  </si>
+  <si>
+    <t>rhteh</t>
   </si>
 </sst>
 </file>
@@ -426,10 +462,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,143 +487,139 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:26">
       <c r="A2">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B2">
-        <v>120176</v>
+        <v>7312641</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>20</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="Q2">
+        <v>15000.0</v>
+      </c>
+      <c r="R2">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>47</v>
-      </c>
-      <c r="B3">
-        <v>141151</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+      <c r="S2">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>57</v>
-      </c>
-      <c r="B4">
-        <v>9150391</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>64</v>
-      </c>
-      <c r="B5">
-        <v>133843</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
+      <c r="V2">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>72</v>
-      </c>
-      <c r="B6">
-        <v>7821991</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>65</v>
-      </c>
-      <c r="B7">
-        <v>214390</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>0.0</v>
+      <c r="W2">
+        <v>15000.0</v>
+      </c>
+      <c r="X2">
+        <v>10000.5</v>
+      </c>
+      <c r="Y2">
+        <v>4999.5</v>
       </c>
     </row>
   </sheetData>
